--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Wed Sep 09 2026 09:59:01</t>
+    <t>Date: Thu Sep 10 2026 14:45:22</t>
   </si>
   <si>
     <t/>
@@ -220,7 +220,7 @@
     <t>Binding Wire</t>
   </si>
   <si>
-    <t>922 Kg</t>
+    <t>746 Kg</t>
   </si>
   <si>
     <t>Bit 1.5in for Drill Bil</t>
@@ -583,7 +583,7 @@
     <t>Curing Compound Sika Antisol</t>
   </si>
   <si>
-    <t>175 Drum</t>
+    <t>173 Drum</t>
   </si>
   <si>
     <t>Curing Pipe 1in</t>
@@ -871,7 +871,7 @@
     <t>Foam Sheet 5mm</t>
   </si>
   <si>
-    <t>409 Nos</t>
+    <t>383 Nos</t>
   </si>
   <si>
     <t>Folding Pipe 10ft</t>
@@ -1891,7 +1891,7 @@
     <t>PC Strand Wire</t>
   </si>
   <si>
-    <t>315 Roll</t>
+    <t>309 Roll</t>
   </si>
   <si>
     <t>PPR Elbow 25mm</t>
@@ -1999,7 +1999,7 @@
     <t>PVC Pipe 1-1/4"</t>
   </si>
   <si>
-    <t>523 Nos</t>
+    <t>462 Nos</t>
   </si>
   <si>
     <t>PVC Pipe 150mm</t>
@@ -2155,7 +2155,7 @@
     <t>Plastic Saddle</t>
   </si>
   <si>
-    <t>518 Nos</t>
+    <t>833 Nos</t>
   </si>
   <si>
     <t>Platform For Gantry</t>
@@ -2722,7 +2722,7 @@
     <t>Stressing block 19/0.5"</t>
   </si>
   <si>
-    <t>158 Nos</t>
+    <t>88 Nos</t>
   </si>
   <si>
     <t>Sunction Pipe 1.5in</t>
@@ -2914,13 +2914,13 @@
     <t>Trumpet Cone 17/0.5in</t>
   </si>
   <si>
-    <t>636 Nos</t>
+    <t>576 Nos</t>
   </si>
   <si>
     <t>Trumpet Cone 4/0.5in</t>
   </si>
   <si>
-    <t>996 Nos</t>
+    <t>968 Nos</t>
   </si>
   <si>
     <t>Trumpet Large Size</t>
@@ -3019,7 +3019,7 @@
     <t>Wedges 0.5"</t>
   </si>
   <si>
-    <t>4019 Nos</t>
+    <t>2829 Nos</t>
   </si>
   <si>
     <t>Weight Scale 100Kg</t>
@@ -3073,7 +3073,7 @@
     <t>Welding Rod 10# (7018)</t>
   </si>
   <si>
-    <t>4 Pkt</t>
+    <t>3 Pkt</t>
   </si>
   <si>
     <t>Welding Rod 12#</t>
@@ -3091,7 +3091,7 @@
     <t>Welding Rod 8#</t>
   </si>
   <si>
-    <t>39 Pkt</t>
+    <t>23 Pkt</t>
   </si>
   <si>
     <t>Welding Rod Holder 1000A</t>
@@ -3184,25 +3184,25 @@
     <t>pvc pipe 1inch</t>
   </si>
   <si>
-    <t>1192 Nos</t>
+    <t>1113 Nos</t>
   </si>
   <si>
     <t>sheet pipe 81mm</t>
   </si>
   <si>
-    <t>848 Nos</t>
+    <t>741 Nos</t>
   </si>
   <si>
     <t>sheet pipe 84mm</t>
   </si>
   <si>
-    <t>148 Nos</t>
+    <t>135 Nos</t>
   </si>
   <si>
     <t>sheet pipe45mm</t>
   </si>
   <si>
-    <t>1759 Nos</t>
+    <t>1384 Nos</t>
   </si>
   <si>
     <t>white cement</t>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Sep 10 2026 14:45:22</t>
+    <t>Date: Thu Sep 10 2026 18:30:46</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Thu Sep 10 2026 18:30:46</t>
+    <t>Date: Fri Sep 11 2026 09:59:01</t>
   </si>
   <si>
     <t/>

--- a/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
+++ b/12 Km bridge over River Indus connecting Ghotki with Kandhkot/InventoryReport.xlsx
@@ -19,7 +19,7 @@
     <t>Inventory Daily Status Report</t>
   </si>
   <si>
-    <t>Date: Fri Sep 11 2026 09:59:01</t>
+    <t>Date: Sat Sep 12 2026 09:59:01</t>
   </si>
   <si>
     <t/>
@@ -220,7 +220,7 @@
     <t>Binding Wire</t>
   </si>
   <si>
-    <t>746 Kg</t>
+    <t>539 Kg</t>
   </si>
   <si>
     <t>Bit 1.5in for Drill Bil</t>
@@ -583,7 +583,7 @@
     <t>Curing Compound Sika Antisol</t>
   </si>
   <si>
-    <t>173 Drum</t>
+    <t>171 Drum</t>
   </si>
   <si>
     <t>Curing Pipe 1in</t>
@@ -871,7 +871,7 @@
     <t>Foam Sheet 5mm</t>
   </si>
   <si>
-    <t>383 Nos</t>
+    <t>364 Nos</t>
   </si>
   <si>
     <t>Folding Pipe 10ft</t>
@@ -1891,7 +1891,7 @@
     <t>PC Strand Wire</t>
   </si>
   <si>
-    <t>309 Roll</t>
+    <t>446 Roll</t>
   </si>
   <si>
     <t>PPR Elbow 25mm</t>
@@ -1999,7 +1999,7 @@
     <t>PVC Pipe 1-1/4"</t>
   </si>
   <si>
-    <t>462 Nos</t>
+    <t>416 Nos</t>
   </si>
   <si>
     <t>PVC Pipe 150mm</t>
@@ -2155,7 +2155,7 @@
     <t>Plastic Saddle</t>
   </si>
   <si>
-    <t>833 Nos</t>
+    <t>808 Nos</t>
   </si>
   <si>
     <t>Platform For Gantry</t>
@@ -2386,6 +2386,9 @@
     <t>Samad Bond</t>
   </si>
   <si>
+    <t>219 Nos</t>
+  </si>
+  <si>
     <t>Sand</t>
   </si>
   <si>
@@ -2722,9 +2725,6 @@
     <t>Stressing block 19/0.5"</t>
   </si>
   <si>
-    <t>88 Nos</t>
-  </si>
-  <si>
     <t>Sunction Pipe 1.5in</t>
   </si>
   <si>
@@ -2914,13 +2914,13 @@
     <t>Trumpet Cone 17/0.5in</t>
   </si>
   <si>
-    <t>576 Nos</t>
+    <t>506 Nos</t>
   </si>
   <si>
     <t>Trumpet Cone 4/0.5in</t>
   </si>
   <si>
-    <t>968 Nos</t>
+    <t>932 Nos</t>
   </si>
   <si>
     <t>Trumpet Large Size</t>
@@ -3019,7 +3019,7 @@
     <t>Wedges 0.5"</t>
   </si>
   <si>
-    <t>2829 Nos</t>
+    <t>1639 Nos</t>
   </si>
   <si>
     <t>Weight Scale 100Kg</t>
@@ -3073,7 +3073,7 @@
     <t>Welding Rod 10# (7018)</t>
   </si>
   <si>
-    <t>3 Pkt</t>
+    <t>1 Pkt</t>
   </si>
   <si>
     <t>Welding Rod 12#</t>
@@ -3091,7 +3091,7 @@
     <t>Welding Rod 8#</t>
   </si>
   <si>
-    <t>23 Pkt</t>
+    <t>14 Pkt</t>
   </si>
   <si>
     <t>Welding Rod Holder 1000A</t>
@@ -3184,25 +3184,25 @@
     <t>pvc pipe 1inch</t>
   </si>
   <si>
-    <t>1113 Nos</t>
+    <t>1045 Nos</t>
   </si>
   <si>
     <t>sheet pipe 81mm</t>
   </si>
   <si>
-    <t>741 Nos</t>
+    <t>591 Nos</t>
   </si>
   <si>
     <t>sheet pipe 84mm</t>
   </si>
   <si>
-    <t>135 Nos</t>
+    <t>122 Nos</t>
   </si>
   <si>
     <t>sheet pipe45mm</t>
   </si>
   <si>
-    <t>1384 Nos</t>
+    <t>1248 Nos</t>
   </si>
   <si>
     <t>white cement</t>
@@ -12287,7 +12287,7 @@
         <v>9</v>
       </c>
       <c r="D621" s="2" t="s">
-        <v>447</v>
+        <v>791</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
@@ -12295,7 +12295,7 @@
         <v>617</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>9</v>
@@ -12309,13 +12309,13 @@
         <v>618</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
@@ -12323,7 +12323,7 @@
         <v>619</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>9</v>
@@ -12337,13 +12337,13 @@
         <v>620</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D625" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
@@ -12351,13 +12351,13 @@
         <v>621</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D626" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
@@ -12365,7 +12365,7 @@
         <v>622</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>9</v>
@@ -12379,7 +12379,7 @@
         <v>623</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>9</v>
@@ -12393,13 +12393,13 @@
         <v>624</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
@@ -12407,7 +12407,7 @@
         <v>625</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>9</v>
@@ -12421,7 +12421,7 @@
         <v>626</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>9</v>
@@ -12435,7 +12435,7 @@
         <v>627</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>9</v>
@@ -12449,7 +12449,7 @@
         <v>628</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>9</v>
@@ -12463,10 +12463,10 @@
         <v>629</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>52</v>
@@ -12477,13 +12477,13 @@
         <v>630</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
@@ -12491,7 +12491,7 @@
         <v>631</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>9</v>
@@ -12505,7 +12505,7 @@
         <v>632</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>9</v>
@@ -12519,7 +12519,7 @@
         <v>633</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>9</v>
@@ -12533,7 +12533,7 @@
         <v>634</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C639" s="2" t="s">
         <v>9</v>
@@ -12547,13 +12547,13 @@
         <v>635</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
@@ -12561,13 +12561,13 @@
         <v>636</v>
       </c>
       <c r="B641" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D641" s="2" t="s">
         <v>817</v>
-      </c>
-      <c r="C641" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D641" s="2" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
@@ -12575,13 +12575,13 @@
         <v>637</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C642" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D642" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
@@ -12589,10 +12589,10 @@
         <v>638</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>12</v>
@@ -12603,7 +12603,7 @@
         <v>639</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>9</v>
@@ -12617,13 +12617,13 @@
         <v>640</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
@@ -12631,13 +12631,13 @@
         <v>641</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
@@ -12645,7 +12645,7 @@
         <v>642</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>9</v>
@@ -12659,7 +12659,7 @@
         <v>643</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>9</v>
@@ -12673,7 +12673,7 @@
         <v>644</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>9</v>
@@ -12687,13 +12687,13 @@
         <v>645</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
@@ -12701,13 +12701,13 @@
         <v>646</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
@@ -12715,13 +12715,13 @@
         <v>647</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C652" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
@@ -12729,7 +12729,7 @@
         <v>648</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>9</v>
@@ -12743,7 +12743,7 @@
         <v>649</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>9</v>
@@ -12757,13 +12757,13 @@
         <v>650</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
@@ -12771,7 +12771,7 @@
         <v>651</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C656" s="2" t="s">
         <v>9</v>
@@ -12785,7 +12785,7 @@
         <v>652</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C657" s="2" t="s">
         <v>9</v>
@@ -12799,13 +12799,13 @@
         <v>653</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C658" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
@@ -12813,7 +12813,7 @@
         <v>654</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>9</v>
@@ -12827,7 +12827,7 @@
         <v>655</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C660" s="2" t="s">
         <v>9</v>
@@ -12841,7 +12841,7 @@
         <v>656</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>9</v>
@@ -12855,7 +12855,7 @@
         <v>657</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C662" s="2" t="s">
         <v>9</v>
@@ -12869,7 +12869,7 @@
         <v>658</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>9</v>
@@ -12883,7 +12883,7 @@
         <v>659</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C664" s="2" t="s">
         <v>9</v>
@@ -12897,13 +12897,13 @@
         <v>660</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
@@ -12911,7 +12911,7 @@
         <v>661</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>9</v>
@@ -12925,7 +12925,7 @@
         <v>662</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>9</v>
@@ -12939,7 +12939,7 @@
         <v>663</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C668" s="2" t="s">
         <v>9</v>
@@ -12953,7 +12953,7 @@
         <v>664</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C669" s="2" t="s">
         <v>9</v>
@@ -12967,7 +12967,7 @@
         <v>665</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>9</v>
@@ -12981,7 +12981,7 @@
         <v>666</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>9</v>
@@ -12995,7 +12995,7 @@
         <v>667</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>9</v>
@@ -13009,7 +13009,7 @@
         <v>668</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>9</v>
@@ -13023,13 +13023,13 @@
         <v>669</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C674" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
@@ -13037,7 +13037,7 @@
         <v>670</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>9</v>
@@ -13051,7 +13051,7 @@
         <v>671</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>9</v>
@@ -13065,13 +13065,13 @@
         <v>672</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
@@ -13079,7 +13079,7 @@
         <v>673</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>9</v>
@@ -13093,7 +13093,7 @@
         <v>674</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>9</v>
@@ -13107,7 +13107,7 @@
         <v>675</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C680" s="2" t="s">
         <v>9</v>
@@ -13121,7 +13121,7 @@
         <v>676</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C681" s="2" t="s">
         <v>9</v>
@@ -13135,13 +13135,13 @@
         <v>677</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
@@ -13149,7 +13149,7 @@
         <v>678</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>9</v>
@@ -13163,7 +13163,7 @@
         <v>679</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C684" s="2" t="s">
         <v>9</v>
@@ -13177,7 +13177,7 @@
         <v>680</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>9</v>
@@ -13191,13 +13191,13 @@
         <v>681</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
@@ -13205,13 +13205,13 @@
         <v>682</v>
       </c>
       <c r="B687" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D687" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="C687" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D687" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
@@ -13219,13 +13219,13 @@
         <v>683</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C688" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
@@ -13233,13 +13233,13 @@
         <v>684</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
@@ -13247,13 +13247,13 @@
         <v>685</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C690" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D690" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
@@ -13261,7 +13261,7 @@
         <v>686</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>9</v>
@@ -13275,7 +13275,7 @@
         <v>687</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>9</v>
@@ -13289,7 +13289,7 @@
         <v>688</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>9</v>
@@ -13303,7 +13303,7 @@
         <v>689</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C694" s="2" t="s">
         <v>9</v>
@@ -13317,7 +13317,7 @@
         <v>690</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>9</v>
@@ -13331,7 +13331,7 @@
         <v>691</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C696" s="2" t="s">
         <v>9</v>
@@ -13345,7 +13345,7 @@
         <v>692</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>9</v>
@@ -13359,7 +13359,7 @@
         <v>693</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>9</v>
@@ -13373,7 +13373,7 @@
         <v>694</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>9</v>
@@ -13387,7 +13387,7 @@
         <v>695</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C700" s="2" t="s">
         <v>9</v>
@@ -13401,7 +13401,7 @@
         <v>696</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>9</v>
@@ -13415,7 +13415,7 @@
         <v>697</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C702" s="2" t="s">
         <v>9</v>
@@ -13429,7 +13429,7 @@
         <v>698</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C703" s="2" t="s">
         <v>9</v>
@@ -13443,7 +13443,7 @@
         <v>699</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C704" s="2" t="s">
         <v>9</v>
@@ -13457,7 +13457,7 @@
         <v>700</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>9</v>
@@ -13471,7 +13471,7 @@
         <v>701</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>9</v>
@@ -13485,13 +13485,13 @@
         <v>702</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C707" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
@@ -13499,7 +13499,7 @@
         <v>703</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>9</v>
@@ -13513,13 +13513,13 @@
         <v>704</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
@@ -13527,7 +13527,7 @@
         <v>705</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>9</v>
@@ -13541,13 +13541,13 @@
         <v>706</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C711" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>903</v>
+        <v>132</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
